--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_11_9.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_11_9.xlsx
@@ -513,1376 +513,1376 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_5</t>
+          <t>model_11_9_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9990682961956155</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6706411192570159</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9991071750768054</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9950330514345993</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9973311489454664</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0005530996257913067</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1955216591718661</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0006055558067063854</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002851316852673949</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001728435002637976</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004870247725418539</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0235180701970061</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N2" t="n">
-        <v>1.00036657198861</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0245192831344094</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P2" t="n">
-        <v>184.9999448350599</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q2" t="n">
-        <v>288.6043899488569</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_4</t>
+          <t>model_11_9_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9990682978961917</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6706411114403619</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9991072035881851</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9950330287406532</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9973311517680622</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005530986162558652</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1955216638121695</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006055364689492378</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002851329880316571</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001728433174632904</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004870245161099471</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02351804873402267</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000366571319531</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02451926075770233</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P3" t="n">
-        <v>184.9999484855283</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q3" t="n">
-        <v>288.6043935993254</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_3</t>
+          <t>model_11_9_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9990682972297973</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6706411083022363</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9991072035881851</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9950330244332458</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9973311498590308</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005530990118563649</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1955216656750964</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006055364689492378</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00285133235301852</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001728434410983879</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004870241689980306</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02351805714459349</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000366571581719</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02451926952632856</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P4" t="n">
-        <v>184.9999470550407</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q4" t="n">
-        <v>288.6043921688378</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_0</t>
+          <t>model_11_9_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9990683013432391</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6706411071938982</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9991072255737125</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9950330250454994</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9973311635518158</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0005530965699395943</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1955216663330537</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0006055215573317297</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002851332001549437</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001728425543089608</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004870246861723988</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02351800522875174</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000366569963316</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02451921540032195</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P5" t="n">
-        <v>184.9999558850046</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q5" t="n">
-        <v>288.6044009988017</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_1</t>
+          <t>model_11_9_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9990683013432391</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6706411071938982</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9991072255737125</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9950330250454994</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9973311635518158</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0005530965699395943</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1955216663330537</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0006055215573317297</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002851332001549437</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001728425543089608</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004870246861723988</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02351800522875174</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000366569963316</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02451921540032195</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P6" t="n">
-        <v>184.9999558850046</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q6" t="n">
-        <v>288.6044009988017</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_2</t>
+          <t>model_11_9_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9990683013432391</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6706411071938982</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9991072255737125</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9950330250454994</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9973311635518158</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0005530965699395943</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1955216663330537</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0006055215573317297</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002851332001549437</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001728425543089608</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004870246861723988</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02351800522875174</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000366569963316</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02451921540032195</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P7" t="n">
-        <v>184.9999558850046</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q7" t="n">
-        <v>288.6044009988017</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_9</t>
+          <t>model_11_9_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.999068294659371</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6706410857586269</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9991071487844341</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9950330725679943</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F8" t="n">
-        <v>0.997331142495027</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0005531005377724563</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1955216790579568</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006055736394277737</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002851304720878241</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001728439180153008</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004870264351600318</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02351808958594333</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000366572593034</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02451930334877383</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P8" t="n">
-        <v>184.9999415373524</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q8" t="n">
-        <v>288.6043866511494</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_10</t>
+          <t>model_11_9_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.999068294659371</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6706410857457046</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9991071487844341</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9950330725679943</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F9" t="n">
-        <v>0.997331142495027</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0005531005377724563</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.195521679065628</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0006055736394277737</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002851304720878241</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001728439180153008</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004870264351600318</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02351808958594333</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000366572593034</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02451930334877383</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P9" t="n">
-        <v>184.9999415373524</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q9" t="n">
-        <v>288.6043866511494</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_11</t>
+          <t>model_11_9_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.999068294659371</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6706410838310833</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9991071487844341</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9950330725679943</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F10" t="n">
-        <v>0.997331142495027</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005531005377724563</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1955216802022299</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0006055736394277737</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.002851304720878241</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001728439180153008</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004870264351600318</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02351808958594333</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000366572593034</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02451930334877383</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P10" t="n">
-        <v>184.9999415373524</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q10" t="n">
-        <v>288.6043866511494</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_22</t>
+          <t>model_11_9_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.999068294659371</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6706410831670176</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9991071487844341</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9950330725679943</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F11" t="n">
-        <v>0.997331142495027</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0005531005377724563</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.195521680596448</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0006055736394277737</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.002851304720878241</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001728439180153008</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004870264351600318</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02351808958594333</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000366572593034</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02451930334877383</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P11" t="n">
-        <v>184.9999415373524</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q11" t="n">
-        <v>288.6043866511494</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_21</t>
+          <t>model_11_9_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.999068294659371</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6706410831670176</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9991071487844341</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9950330725679943</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F12" t="n">
-        <v>0.997331142495027</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0005531005377724563</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.195521680596448</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0006055736394277737</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.002851304720878241</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001728439180153008</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.004870264351600318</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02351808958594333</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000366572593034</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02451930334877383</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P12" t="n">
-        <v>184.9999415373524</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q12" t="n">
-        <v>288.6043866511494</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_20</t>
+          <t>model_11_9_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.999068294659371</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6706410831670176</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9991071487844341</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9950330725679943</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F13" t="n">
-        <v>0.997331142495027</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0005531005377724563</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.195521680596448</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0006055736394277737</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.002851304720878241</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.001728439180153008</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004870264351600318</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02351808958594333</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000366572593034</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02451930334877383</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P13" t="n">
-        <v>184.9999415373524</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q13" t="n">
-        <v>288.6043866511494</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_19</t>
+          <t>model_11_9_12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.999068294659371</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6706410831670176</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9991071487844341</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9950330725679943</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F14" t="n">
-        <v>0.997331142495027</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0005531005377724563</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.195521680596448</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0006055736394277737</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.002851304720878241</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001728439180153008</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.004870264351600318</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02351808958594333</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000366572593034</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02451930334877383</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P14" t="n">
-        <v>184.9999415373524</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q14" t="n">
-        <v>288.6043866511494</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_18</t>
+          <t>model_11_9_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.999068294659371</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6706410831670176</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9991071487844341</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9950330725679943</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.997331142495027</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0005531005377724563</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.195521680596448</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0006055736394277737</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.002851304720878241</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.001728439180153008</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.004870264351600318</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M15" t="n">
-        <v>0.02351808958594333</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000366572593034</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O15" t="n">
-        <v>0.02451930334877383</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P15" t="n">
-        <v>184.9999415373524</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q15" t="n">
-        <v>288.6043866511494</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_17</t>
+          <t>model_11_9_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.999068294659371</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6706410831670176</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9991071487844341</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9950330725679943</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F16" t="n">
-        <v>0.997331142495027</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0005531005377724563</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.195521680596448</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0006055736394277737</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.002851304720878241</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001728439180153008</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.004870264351600318</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M16" t="n">
-        <v>0.02351808958594333</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000366572593034</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02451930334877383</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P16" t="n">
-        <v>184.9999415373524</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q16" t="n">
-        <v>288.6043866511494</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_16</t>
+          <t>model_11_9_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.999068294659371</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6706410831670176</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9991071487844341</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9950330725679943</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F17" t="n">
-        <v>0.997331142495027</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0005531005377724563</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.195521680596448</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0006055736394277737</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.002851304720878241</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001728439180153008</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.004870264351600318</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M17" t="n">
-        <v>0.02351808958594333</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000366572593034</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O17" t="n">
-        <v>0.02451930334877383</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P17" t="n">
-        <v>184.9999415373524</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q17" t="n">
-        <v>288.6043866511494</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_12</t>
+          <t>model_11_9_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.999068294659371</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6706410831670176</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9991071487844341</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9950330725679943</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F18" t="n">
-        <v>0.997331142495027</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0005531005377724563</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.195521680596448</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0006055736394277737</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.002851304720878241</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001728439180153008</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.004870264351600318</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M18" t="n">
-        <v>0.02351808958594333</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000366572593034</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O18" t="n">
-        <v>0.02451930334877383</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P18" t="n">
-        <v>184.9999415373524</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q18" t="n">
-        <v>288.6043866511494</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_14</t>
+          <t>model_11_9_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.999068294659371</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6706410831670176</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9991071487844341</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9950330725679943</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F19" t="n">
-        <v>0.997331142495027</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0005531005377724563</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.195521680596448</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0006055736394277737</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.002851304720878241</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>0.001728439180153008</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.004870264351600318</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M19" t="n">
-        <v>0.02351808958594333</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000366572593034</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O19" t="n">
-        <v>0.02451930334877383</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P19" t="n">
-        <v>184.9999415373524</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q19" t="n">
-        <v>288.6043866511494</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_13</t>
+          <t>model_11_9_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.999068294659371</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6706410831670176</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9991071487844341</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9950330725679943</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F20" t="n">
-        <v>0.997331142495027</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0005531005377724563</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.195521680596448</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0006055736394277737</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.002851304720878241</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.001728439180153008</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.004870264351600318</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M20" t="n">
-        <v>0.02351808958594333</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000366572593034</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O20" t="n">
-        <v>0.02451930334877383</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P20" t="n">
-        <v>184.9999415373524</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q20" t="n">
-        <v>288.6043866511494</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_23</t>
+          <t>model_11_9_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.999068294659371</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6706410831670176</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9991071487844341</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9950330725679943</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F21" t="n">
-        <v>0.997331142495027</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0005531005377724563</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.195521680596448</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0006055736394277737</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.002851304720878241</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.001728439180153008</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.004870264351600318</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M21" t="n">
-        <v>0.02351808958594333</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000366572593034</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O21" t="n">
-        <v>0.02451930334877383</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P21" t="n">
-        <v>184.9999415373524</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q21" t="n">
-        <v>288.6043866511494</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_15</t>
+          <t>model_11_9_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.999068294659371</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6706410831670176</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9991071487844341</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9950330725679943</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F22" t="n">
-        <v>0.997331142495027</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0005531005377724563</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.195521680596448</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0006055736394277737</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.002851304720878241</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.001728439180153008</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.004870264351600318</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M22" t="n">
-        <v>0.02351808958594333</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000366572593034</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O22" t="n">
-        <v>0.02451930334877383</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P22" t="n">
-        <v>184.9999415373524</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q22" t="n">
-        <v>288.6043866511494</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_24</t>
+          <t>model_11_9_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.999068294659371</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6706410831670176</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9991071487844341</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9950330725679943</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F23" t="n">
-        <v>0.997331142495027</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0005531005377724563</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.195521680596448</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0006055736394277737</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.002851304720878241</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.001728439180153008</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.004870264351600318</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M23" t="n">
-        <v>0.02351808958594333</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000366572593034</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O23" t="n">
-        <v>0.02451930334877383</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P23" t="n">
-        <v>184.9999415373524</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q23" t="n">
-        <v>288.6043866511494</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_8</t>
+          <t>model_11_9_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9990682974663448</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6706410538160003</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9991071604950377</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9950330768753523</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9973311486271157</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0005530988714315107</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1955216980204798</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0006055656967462595</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.002851302248204713</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.00172843520881225</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.004870293258483868</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M24" t="n">
-        <v>0.02351805415912445</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000366571488651</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O24" t="n">
-        <v>0.02451926641376192</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P24" t="n">
-        <v>184.9999475628155</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q24" t="n">
-        <v>288.6043926766126</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_7</t>
+          <t>model_11_9_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9990682941017778</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6706410480164398</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9991071604950377</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9950330551296789</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F25" t="n">
-        <v>0.997331138989492</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0005531008687838435</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1955217014633494</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0006055656967462595</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.002851314731483716</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.001728441450451752</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.004870303334908521</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0235180966233206</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000366572812415</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O25" t="n">
-        <v>0.02451931068574681</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P25" t="n">
-        <v>184.9999403404225</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q25" t="n">
-        <v>288.6043854542195</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_6</t>
+          <t>model_11_9_24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9990682941017778</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6706410480164398</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9991071604950377</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9950330551296789</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F26" t="n">
-        <v>0.997331138989492</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0005531008687838435</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1955217014633494</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0006055656967462595</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.002851314731483716</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.001728441450451752</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.004870303334908521</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0235180966233206</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000366572812415</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O26" t="n">
-        <v>0.02451931068574681</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P26" t="n">
-        <v>184.9999403404225</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q26" t="n">
-        <v>288.6043854542195</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
   </sheetData>
